--- a/day1/Monday_Day1_Import_Pack.xlsx
+++ b/day1/Monday_Day1_Import_Pack.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Marketing Board Import" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Venue Pipeline Import" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Team Availability Import" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Targets Import" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Main Board Import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Now Review (agree on the day)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Venue Pipeline Import" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Team Invites (confirm)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,13 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,25 +471,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>When</t>
+          <t>Timing (as planned)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Due date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested owner (from notes - confirm)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Task ID</t>
         </is>
@@ -524,18 +536,28 @@
           <t>Fri 2 Oct</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Cat – from the van</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -570,18 +592,28 @@
           <t>Fri 2 Oct</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Cat – call Charlotte for card</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -616,18 +648,28 @@
           <t>Fri 2 Oct</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Cat to email him once done</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -662,14 +704,20 @@
           <t>Fri 2 Oct</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -705,17 +753,19 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>This workbook covers the task list</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -750,14 +800,20 @@
           <t>Mon 5 Oct</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -792,18 +848,28 @@
           <t>Mon 5 Oct</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Yahya</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -838,18 +904,28 @@
           <t>Mon 5 Oct</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Yahya</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -884,18 +960,28 @@
           <t>Mon 5 Oct</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Yahya</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -931,17 +1017,23 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Yahya</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -977,13 +1069,15 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1019,13 +1113,15 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1061,13 +1157,15 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1103,13 +1201,15 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1145,13 +1245,15 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1187,13 +1289,15 @@
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1229,13 +1333,15 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1271,17 +1377,19 @@
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>First job when Lois starts</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1317,13 +1425,15 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1359,13 +1469,15 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1401,13 +1513,15 @@
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1443,13 +1557,15 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1485,13 +1601,15 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1527,17 +1645,23 @@
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Cat + Lois brainstorm</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1573,13 +1697,15 @@
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1615,13 +1741,15 @@
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1657,13 +1785,15 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1699,17 +1829,19 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Use BNC's marketing systems</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1745,13 +1877,15 @@
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1787,17 +1921,19 @@
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Date TBC – end of October</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1833,13 +1969,15 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1875,13 +2013,15 @@
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1917,13 +2057,15 @@
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1959,13 +2101,15 @@
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2001,13 +2145,15 @@
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
         <v>35</v>
       </c>
     </row>
@@ -2043,13 +2189,15 @@
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2085,13 +2233,15 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2127,13 +2277,15 @@
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2169,13 +2321,15 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
         <v>39</v>
       </c>
     </row>
@@ -2211,13 +2365,15 @@
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2253,13 +2409,15 @@
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2295,13 +2453,15 @@
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
         <v>42</v>
       </c>
     </row>
@@ -2337,17 +2497,19 @@
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Whole Collective as one supplier: food, drink, styling, staffing, wellness, Latino</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>43</v>
       </c>
     </row>
@@ -2383,13 +2545,15 @@
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
         <v>44</v>
       </c>
     </row>
@@ -2425,13 +2589,15 @@
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
         <v>45</v>
       </c>
     </row>
@@ -2467,13 +2633,15 @@
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
         <v>46</v>
       </c>
     </row>
@@ -2509,13 +2677,15 @@
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
         <v>47</v>
       </c>
     </row>
@@ -2551,17 +2721,19 @@
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Link with PenniBlack Christmas packages</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>48</v>
       </c>
     </row>
@@ -2597,13 +2769,15 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
         <v>49</v>
       </c>
     </row>
@@ -2639,13 +2813,15 @@
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2681,13 +2857,15 @@
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="n">
         <v>51</v>
       </c>
     </row>
@@ -2723,17 +2901,19 @@
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Use Free Spirit at Menier as the model</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>52</v>
       </c>
     </row>
@@ -2769,13 +2949,15 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="n">
         <v>53</v>
       </c>
     </row>
@@ -2811,13 +2993,15 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2852,18 +3036,24 @@
           <t>Mon 5 Oct</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Ask Yahya</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2899,13 +3089,15 @@
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2941,17 +3133,19 @@
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Big follower base – use it</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>57</v>
       </c>
     </row>
@@ -2987,13 +3181,15 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
         <v>58</v>
       </c>
     </row>
@@ -3029,13 +3225,15 @@
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="n">
         <v>59</v>
       </c>
     </row>
@@ -3071,13 +3269,15 @@
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3113,17 +3313,23 @@
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Danelle + Ana</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Danelle + Ana</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3159,13 +3365,15 @@
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="n">
         <v>62</v>
       </c>
     </row>
@@ -3201,13 +3409,15 @@
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="n">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3243,13 +3453,15 @@
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="n">
         <v>64</v>
       </c>
     </row>
@@ -3285,13 +3497,15 @@
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
         <v>65</v>
       </c>
     </row>
@@ -3327,13 +3541,15 @@
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
         <v>66</v>
       </c>
     </row>
@@ -3369,13 +3585,15 @@
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
         <v>67</v>
       </c>
     </row>
@@ -3411,17 +3629,19 @@
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Hoping for Wed 21 Oct</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>68</v>
       </c>
     </row>
@@ -3457,17 +3677,19 @@
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Purpose: the Menier team try it and review it</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>69</v>
       </c>
     </row>
@@ -3503,17 +3725,19 @@
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Waiting on date</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>70</v>
       </c>
     </row>
@@ -3549,13 +3773,15 @@
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="n">
         <v>71</v>
       </c>
     </row>
@@ -3591,17 +3817,19 @@
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Luxury experience is the brief</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>72</v>
       </c>
     </row>
@@ -3637,13 +3865,15 @@
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="n">
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="n">
         <v>73</v>
       </c>
     </row>
@@ -3679,13 +3909,15 @@
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="n">
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="n">
         <v>74</v>
       </c>
     </row>
@@ -3721,13 +3953,15 @@
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="n">
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
         <v>75</v>
       </c>
     </row>
@@ -3763,13 +3997,15 @@
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="n">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="n">
         <v>76</v>
       </c>
     </row>
@@ -3805,13 +4041,15 @@
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="n">
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="n">
         <v>77</v>
       </c>
     </row>
@@ -3847,13 +4085,15 @@
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="n">
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="n">
         <v>78</v>
       </c>
     </row>
@@ -3889,13 +4129,15 @@
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="n">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="n">
         <v>79</v>
       </c>
     </row>
@@ -3930,18 +4172,24 @@
           <t>Mon 5 Oct</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>Promised in Charlotte's email of 1 Oct – Cat</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="L81" t="n">
         <v>80</v>
       </c>
     </row>
@@ -3977,17 +4225,19 @@
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>Quick win</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>81</v>
       </c>
     </row>
@@ -4023,13 +4273,15 @@
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="n">
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="n">
         <v>82</v>
       </c>
     </row>
@@ -4065,13 +4317,15 @@
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="n">
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="n">
         <v>83</v>
       </c>
     </row>
@@ -4107,13 +4361,15 @@
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="n">
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4149,13 +4405,15 @@
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="n">
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="n">
         <v>85</v>
       </c>
     </row>
@@ -4191,13 +4449,15 @@
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="n">
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="n">
         <v>86</v>
       </c>
     </row>
@@ -4233,13 +4493,15 @@
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="n">
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="n">
         <v>87</v>
       </c>
     </row>
@@ -4275,13 +4537,15 @@
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="n">
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="n">
         <v>88</v>
       </c>
     </row>
@@ -4317,13 +4581,15 @@
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="n">
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="n">
         <v>89</v>
       </c>
     </row>
@@ -4359,13 +4625,15 @@
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="n">
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
         <v>90</v>
       </c>
     </row>
@@ -4401,13 +4669,15 @@
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="n">
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="n">
         <v>91</v>
       </c>
     </row>
@@ -4443,13 +4713,15 @@
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="n">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
         <v>92</v>
       </c>
     </row>
@@ -4485,13 +4757,15 @@
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="n">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="n">
         <v>93</v>
       </c>
     </row>
@@ -4527,13 +4801,15 @@
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="n">
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="n">
         <v>94</v>
       </c>
     </row>
@@ -4569,13 +4845,15 @@
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="n">
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
         <v>95</v>
       </c>
     </row>
@@ -4611,13 +4889,15 @@
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="n">
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4653,13 +4933,15 @@
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="n">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="n">
         <v>97</v>
       </c>
     </row>
@@ -4695,13 +4977,15 @@
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="n">
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
         <v>98</v>
       </c>
     </row>
@@ -4737,13 +5021,15 @@
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="n">
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4779,17 +5065,19 @@
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>Separate from Youth</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4825,13 +5113,15 @@
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="n">
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
         <v>101</v>
       </c>
     </row>
@@ -4867,13 +5157,15 @@
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="n">
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="n">
         <v>102</v>
       </c>
     </row>
@@ -4909,13 +5201,15 @@
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="n">
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
         <v>103</v>
       </c>
     </row>
@@ -4951,13 +5245,15 @@
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="n">
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
         <v>104</v>
       </c>
     </row>
@@ -4993,13 +5289,15 @@
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="n">
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="n">
         <v>105</v>
       </c>
     </row>
@@ -5035,13 +5333,15 @@
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="n">
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
         <v>106</v>
       </c>
     </row>
@@ -5077,17 +5377,19 @@
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>Check details with Charlotte</t>
         </is>
       </c>
-      <c r="J108" t="n">
+      <c r="L108" t="n">
         <v>107</v>
       </c>
     </row>
@@ -5123,13 +5425,15 @@
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="n">
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
         <v>108</v>
       </c>
     </row>
@@ -5165,13 +5469,15 @@
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="n">
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="n">
         <v>109</v>
       </c>
     </row>
@@ -5207,13 +5513,15 @@
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="n">
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
         <v>110</v>
       </c>
     </row>
@@ -5249,13 +5557,15 @@
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="n">
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="n">
         <v>111</v>
       </c>
     </row>
@@ -5291,13 +5601,15 @@
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="n">
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
         <v>112</v>
       </c>
     </row>
@@ -5333,13 +5645,15 @@
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="n">
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
         <v>113</v>
       </c>
     </row>
@@ -5375,17 +5689,19 @@
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>Separate from Kids</t>
         </is>
       </c>
-      <c r="J115" t="n">
+      <c r="L115" t="n">
         <v>114</v>
       </c>
     </row>
@@ -5421,13 +5737,15 @@
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
         <v>115</v>
       </c>
     </row>
@@ -5463,13 +5781,15 @@
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="n">
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
         <v>116</v>
       </c>
     </row>
@@ -5505,13 +5825,15 @@
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
         <v>117</v>
       </c>
     </row>
@@ -5547,13 +5869,15 @@
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="n">
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
         <v>118</v>
       </c>
     </row>
@@ -5589,13 +5913,15 @@
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="n">
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
         <v>119</v>
       </c>
     </row>
@@ -5631,13 +5957,15 @@
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="n">
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5673,13 +6001,15 @@
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="n">
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
         <v>121</v>
       </c>
     </row>
@@ -5715,13 +6045,15 @@
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="n">
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
         <v>122</v>
       </c>
     </row>
@@ -5757,17 +6089,19 @@
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>'You've seen it here first'</t>
         </is>
       </c>
-      <c r="J124" t="n">
+      <c r="L124" t="n">
         <v>123</v>
       </c>
     </row>
@@ -5803,13 +6137,15 @@
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="n">
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
         <v>124</v>
       </c>
     </row>
@@ -5845,13 +6181,15 @@
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="n">
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="n">
         <v>125</v>
       </c>
     </row>
@@ -5887,13 +6225,15 @@
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="n">
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="n">
         <v>126</v>
       </c>
     </row>
@@ -5929,13 +6269,15 @@
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="n">
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
         <v>127</v>
       </c>
     </row>
@@ -5971,17 +6313,19 @@
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>Quick win – ask Yahya</t>
         </is>
       </c>
-      <c r="J129" t="n">
+      <c r="L129" t="n">
         <v>128</v>
       </c>
     </row>
@@ -6017,17 +6361,23 @@
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Yahya</t>
         </is>
       </c>
-      <c r="J130" t="n">
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
         <v>129</v>
       </c>
     </row>
@@ -6063,13 +6413,15 @@
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="n">
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
         <v>130</v>
       </c>
     </row>
@@ -6105,13 +6457,15 @@
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="n">
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="n">
         <v>131</v>
       </c>
     </row>
@@ -6147,17 +6501,23 @@
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="J133" t="n">
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
         <v>132</v>
       </c>
     </row>
@@ -6193,13 +6553,15 @@
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="n">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="n">
         <v>133</v>
       </c>
     </row>
@@ -6235,13 +6597,15 @@
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="n">
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
         <v>134</v>
       </c>
     </row>
@@ -6277,13 +6641,15 @@
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="n">
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="n">
         <v>135</v>
       </c>
     </row>
@@ -6319,17 +6685,23 @@
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Yahya</t>
         </is>
       </c>
-      <c r="J137" t="n">
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
         <v>136</v>
       </c>
     </row>
@@ -6365,13 +6737,15 @@
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="n">
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="n">
         <v>137</v>
       </c>
     </row>
@@ -6407,13 +6781,15 @@
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="n">
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="n">
         <v>138</v>
       </c>
     </row>
@@ -6428,10 +6804,868 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Timing (as planned)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed due date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmed in Now? (Y/N)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Agreed due date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Check Monday trial status and end date</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fri 2 Oct</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cat – from the van</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Upgrade Monday to Pro, monthly billing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fri 2 Oct</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Cat – call Charlotte for card</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Invite Yahya to Monday as Member (info@infovis.co.uk)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fri 2 Oct</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cat to email him once done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Make sure Cat is a Monday admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fri 2 Oct</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Send Yahya samples: spreadsheet, task list, marketing plan, targets, enquiry tracker extract</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>This workbook covers the task list</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Setup day with Yahya, Cat and Charlotte</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Build marketing board – one group per brand</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Load this task list into Monday</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0. Monday &amp; Claude Setup</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Build goals &amp; targets dashboard for the Tuesday meeting</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yahya</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1. All Brands</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Include BNC in every press release, for every brand</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Use BNC's marketing systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1b. BNC Exhibition (end Oct)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Confirm exhibition date, venue, stand size and what's included</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Date TBC – end of October</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1b. BNC Exhibition (end Oct)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Find out what marketing BNC offers exhibitors – newsletters, social, website listings, press</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1b. BNC Exhibition (end Oct)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Get BNC logos, brand guidelines and exhibitor wording</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1b. BNC Exhibition (end Oct)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Decide which brands we showcase and how – one Collective stand</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>43</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1c. Venue Sourcing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brainstorm our point of difference – every caterer wants the venues, why us? (Cat, Jessica, Lois)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Whole Collective as one supplier: food, drink, styling, staffing, wellness, Latino</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1c. Venue Sourcing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Write the point of difference in one line, plus 3 proof points</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>45</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1c. Venue Sourcing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Build the target venue list – type, capacity, current caterer, contact</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1c. Venue Sourcing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Christmas packages for venues</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Link with PenniBlack Christmas packages</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>55</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1c. Venue Sourcing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Venue pipeline board in Monday – contacted, meeting, trial, on supplier list</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ask Yahya</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>57</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2. PenniBlack Catering &amp; Events</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Christmas campaign to existing followers – social posts</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oct–Dec</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Big follower base – use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>59</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2. PenniBlack Catering &amp; Events</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Christmas packages with 'from £' prices</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>68</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3. Free Spirit Wellness</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chase Momoko (Menier Venues) to confirm the date – push hard, nothing can be booked until it's set</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Hoping for Wed 21 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>69</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3. Free Spirit Wellness</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Confirm which Menier team members are coming and agree the run of show</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Once date set</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Purpose: the Menier team try it and review it</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>70</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3. Free Spirit Wellness</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Book workshop hosts – Ayurvedic scrubs, yoga, self-defence</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Once date set</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Waiting on date</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4. Pichi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Send Momoko (Menier Venues) the full attendee list from the Pichi launch</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Promised in Charlotte's email of 1 Oct – Cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9. Systems &amp; Admin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Team availability calendar in Monday – who's free to work when</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Quick win – ask Yahya</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6448,7 +7682,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Group (stage - CONFIRM)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -6510,7 +7744,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Target list (not yet contacted)</t>
+          <t>Contacted</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6532,7 +7766,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Contacted</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6554,7 +7788,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6576,7 +7810,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trial / tasting</t>
+          <t>On supplier list</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6594,575 +7828,6 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>On supplier list</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(example - delete) Venue name</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Not a fit / parked</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>(example - delete) Venue name</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Item (Person)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Starts</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Monday access</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Outside the admin system / TBC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Seat</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Starts</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cat (Catrin Dimond)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Chief of Marketing – runs Monday</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Yes – Admin</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lois Burton</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Content, PR &amp; Creative Lead</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>End of October</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jessica</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sales &amp; Events Manager</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mid-October</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Danelle van Tonder</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Quotes &amp; Client Liaison</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ana</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Quotes &amp; Client Support (part-time)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Outside the admin system / TBC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Systems &amp; Events (flexible)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>When free</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Outside the admin system / TBC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Raquel</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Event Manager &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>View only / later</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Core team</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Yahya (InfoVis)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>IT &amp; Database Consultant</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Mon 5 Oct</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Outside the admin system / TBC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Jess &amp; Dave</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Collective partners – design</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Availability to be confirmed with each person</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7175,648 +7840,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item (Brand)</t>
+          <t>Seat</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Monday role planned</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Target: enquiries</t>
+          <t>Starts</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Target: bookings</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Target: £ booked</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Actual: enquiries</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Actual: bookings</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Actual: £ booked</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Invite on Day 1? (confirm)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PenniBlack Catering &amp; Events</t>
+          <t>Seat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Starts</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Free Spirit Wellness</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Cat (Catrin Dimond)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pichi</t>
+          <t>Chief of Marketing – runs Monday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Yes – Admin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Lois Burton</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Raquel's Staffing &amp; Bar</t>
+          <t>Content, PR &amp; Creative Lead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>End of October</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VENN Productions</t>
+          <t>Sales &amp; Events Manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mid-October</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Danelle van Tonder</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Be-Zing Kids</t>
+          <t>Quotes &amp; Client Liaison</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Be-Zing Youth</t>
+          <t>Quotes &amp; Client Support (part-time)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Venue Sourcing</t>
+          <t>Systems &amp; Events (flexible)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>When free</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>Raquel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PenniBlack Catering &amp; Events</t>
+          <t>Event Manager &amp; Logistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>View only / later</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>Yahya (InfoVis)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Free Spirit Wellness</t>
+          <t>IT &amp; Database Consultant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mon 5 Oct</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>Jess &amp; Dave</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pichi</t>
+          <t>Collective partners – design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Raquel's Staffing &amp; Bar</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VENN Productions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Be-Zing Kids</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Be-Zing Youth</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Venue Sourcing</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PenniBlack Catering &amp; Events</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Free Spirit Wellness</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Pichi</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Raquel's Staffing &amp; Bar</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>VENN Productions</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Be-Zing Kids</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Be-Zing Youth</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Venue Sourcing</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
